--- a/output/BackwaterIssues20251010.xlsx
+++ b/output/BackwaterIssues20251010.xlsx
@@ -1,197 +1,218 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\BackwaterGenetics\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECCF539-11D0-4A66-AD5A-81C9F511E3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ContactsNoNFWG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="BadScanUploads" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PondHoppers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ScannedWithoutTagging" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ContactsNoNFWG" sheetId="1" r:id="rId1"/>
+    <sheet name="BadScanUploads" sheetId="2" r:id="rId2"/>
+    <sheet name="PondHoppers" sheetId="3" r:id="rId3"/>
+    <sheet name="ScannedWithoutTagging" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
-  <si>
-    <t xml:space="preserve">PIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MinScanDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxScanDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">001592AEEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPCA (Pond 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0015AC2B4D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPCA (Pond 6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003BC0E3E3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPCA (Pond 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003D4BC4A8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003D795EA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003DF727C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yuma Cove backwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">013BCB7959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">017799077F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deploy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retrieve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnitType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MidDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScanTimeHrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeployedHrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScanMonth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScanMonthName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MinScan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxScan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EffectiveScanHrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScanFY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unknown Pond 5 inflow; Fan is not running, batteries appear to be good; not able to complete download</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPCA (Pond 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shore based</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bad battery Stopped scanning 05/19/24, battery replaced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PITIndex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FirstLocation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecondLocation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FirstEID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FirstContacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FirstDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecondContacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecondDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecondEID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003BE8F3CF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003BFC25A5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003D4F43E7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPCA (Pond 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003D795EAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScanDAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003D770FE9</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>Backwater</t>
+  </si>
+  <si>
+    <t>MinScanDate</t>
+  </si>
+  <si>
+    <t>MaxScanDate</t>
+  </si>
+  <si>
+    <t>contacts</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>001592AEEE</t>
+  </si>
+  <si>
+    <t>IPCA (Pond 2)</t>
+  </si>
+  <si>
+    <t>0015AC2B4D</t>
+  </si>
+  <si>
+    <t>IPCA (Pond 6)</t>
+  </si>
+  <si>
+    <t>003BC0E3E3</t>
+  </si>
+  <si>
+    <t>IPCA (Pond 5)</t>
+  </si>
+  <si>
+    <t>003D4BC4A8</t>
+  </si>
+  <si>
+    <t>003D795EA1</t>
+  </si>
+  <si>
+    <t>003DF727C3</t>
+  </si>
+  <si>
+    <t>Yuma Cove backwater</t>
+  </si>
+  <si>
+    <t>013BCB7959</t>
+  </si>
+  <si>
+    <t>017799077F</t>
+  </si>
+  <si>
+    <t>EID</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Deploy</t>
+  </si>
+  <si>
+    <t>Retrieve</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>UnitType</t>
+  </si>
+  <si>
+    <t>MidDate</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>ScanTimeHrs</t>
+  </si>
+  <si>
+    <t>DeployedHrs</t>
+  </si>
+  <si>
+    <t>ScanMonth</t>
+  </si>
+  <si>
+    <t>ScanMonthName</t>
+  </si>
+  <si>
+    <t>Contacts</t>
+  </si>
+  <si>
+    <t>MinScan</t>
+  </si>
+  <si>
+    <t>MaxScan</t>
+  </si>
+  <si>
+    <t>EffectiveScanHrs</t>
+  </si>
+  <si>
+    <t>ScanFY</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Grey Box</t>
+  </si>
+  <si>
+    <t>unknown Pond 5 inflow; Fan is not running, batteries appear to be good; not able to complete download</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>IPCA (Pond 3)</t>
+  </si>
+  <si>
+    <t>shore based</t>
+  </si>
+  <si>
+    <t>bad battery Stopped scanning 05/19/24, battery replaced.</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>PITIndex</t>
+  </si>
+  <si>
+    <t>FirstLocation</t>
+  </si>
+  <si>
+    <t>SecondLocation</t>
+  </si>
+  <si>
+    <t>FirstEID</t>
+  </si>
+  <si>
+    <t>FirstContacts</t>
+  </si>
+  <si>
+    <t>FirstDate</t>
+  </si>
+  <si>
+    <t>SecondContacts</t>
+  </si>
+  <si>
+    <t>SecondDate</t>
+  </si>
+  <si>
+    <t>SecondEID</t>
+  </si>
+  <si>
+    <t>003BE8F3CF</t>
+  </si>
+  <si>
+    <t>003BFC25A5</t>
+  </si>
+  <si>
+    <t>003D4F43E7</t>
+  </si>
+  <si>
+    <t>IPCA (Pond 1)</t>
+  </si>
+  <si>
+    <t>003D795EAE</t>
+  </si>
+  <si>
+    <t>ScanDAL</t>
+  </si>
+  <si>
+    <t>003D770FE9</t>
   </si>
 </sst>
 </file>
@@ -199,9 +220,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -237,13 +258,22 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -525,11 +555,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,178 +579,178 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>42870</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="1">
         <v>43039</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>169</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1">
         <v>42835</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="1">
         <v>43132</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>44</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>297</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="1">
         <v>43066</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="1">
         <v>43423</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>357</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>44642</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="1">
         <v>45549</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>174</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>907</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>43807</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="1">
         <v>44062</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>173</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>255</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="1">
         <v>44851</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="1">
         <v>45509</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>658</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="1">
         <v>43604</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="1">
         <v>43742</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>6</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>138</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="1">
         <v>42450</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="1">
         <v>42704</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>254</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -773,18 +803,18 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>17626</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>44356.358912037</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>44538.6584027778</v>
+      <c r="C2" s="2">
+        <v>44356.358912037002</v>
+      </c>
+      <c r="D2" s="2">
+        <v>44538.658402777801</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -792,52 +822,52 @@
       <c r="F2" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>44447</v>
       </c>
       <c r="H2" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="n">
-        <v>4376.18333333333</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="I2">
+        <v>4376.1833333333298</v>
+      </c>
+      <c r="J2">
         <v>4375.18777777778</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>9</v>
       </c>
       <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>42</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="1">
         <v>44321</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="1">
         <v>44521</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>4800</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>2021</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>20679</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>45421.5558333333</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>45454.6212037037</v>
+      <c r="C3" s="2">
+        <v>45421.555833333303</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45454.621203703697</v>
       </c>
       <c r="E3" t="s">
         <v>35</v>
@@ -845,52 +875,57 @@
       <c r="F3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45438</v>
       </c>
       <c r="H3" t="s">
         <v>41</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>477.8</v>
       </c>
-      <c r="J3" t="n">
-        <v>793.568888888889</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="J3">
+        <v>793.56888888888898</v>
+      </c>
+      <c r="K3">
         <v>5</v>
       </c>
       <c r="L3" t="s">
         <v>42</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>39</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="1">
         <v>45343</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="1">
         <v>45431</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>2112</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>2024</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -919,7 +954,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -929,26 +964,26 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>13600</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="1">
         <v>43209</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>605</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="1">
         <v>43191</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>12846</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -958,26 +993,26 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>19584</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>118</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="1">
         <v>45034</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="1">
         <v>45704</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>21641</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -987,26 +1022,26 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>13457</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="1">
         <v>43447</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="1">
         <v>43516</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>13458</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1016,37 +1051,37 @@
       <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>14885</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="1">
         <v>43822</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="1">
         <v>43873</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>15071</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -1066,28 +1101,28 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>45159</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="1">
         <v>45530</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>9</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>371</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>